--- a/Output Data Tables/AFAT Outputs/Aggregated Tables/2018/Airline_Cumulative_Financial_Statistics_2018.xlsx
+++ b/Output Data Tables/AFAT Outputs/Aggregated Tables/2018/Airline_Cumulative_Financial_Statistics_2018.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44" uniqueCount="44">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -178,7 +190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -204,49 +216,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1404,48 +1416,248 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>98809474250</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0.1353</v>
+      </c>
+      <c r="D25" s="0">
+        <v>199.91999999999999</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0.1608</v>
+      </c>
+      <c r="F25" s="0">
+        <v>238.33000000000001</v>
+      </c>
+      <c r="G25" s="0">
+        <v>104786038300</v>
+      </c>
+      <c r="H25" s="0">
+        <v>0.1434</v>
+      </c>
+      <c r="I25" s="0">
+        <v>212.00999999999999</v>
+      </c>
+      <c r="J25" s="0">
+        <v>0.17050000000000001</v>
+      </c>
+      <c r="K25" s="0">
+        <v>252.74000000000001</v>
+      </c>
+      <c r="L25" s="0">
+        <v>277826</v>
+      </c>
+      <c r="M25" s="0">
+        <v>2629426</v>
+      </c>
+      <c r="N25" s="0">
+        <v>133865</v>
+      </c>
+      <c r="O25" s="0">
+        <v>377164</v>
+      </c>
+      <c r="P25" s="0">
+        <v>19.640000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>34385396390</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0.1163</v>
+      </c>
+      <c r="D26" s="0">
+        <v>109.13</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0.1386</v>
+      </c>
+      <c r="F26" s="0">
+        <v>134.37</v>
+      </c>
+      <c r="G26" s="0">
+        <v>38707192280</v>
+      </c>
+      <c r="H26" s="0">
+        <v>0.13089999999999999</v>
+      </c>
+      <c r="I26" s="0">
+        <v>122.84999999999999</v>
+      </c>
+      <c r="J26" s="0">
+        <v>0.156</v>
+      </c>
+      <c r="K26" s="0">
+        <v>151.25999999999999</v>
+      </c>
+      <c r="L26" s="0">
+        <v>98754</v>
+      </c>
+      <c r="M26" s="0">
+        <v>2995042</v>
+      </c>
+      <c r="N26" s="0">
+        <v>133106</v>
+      </c>
+      <c r="O26" s="0">
+        <v>391956</v>
+      </c>
+      <c r="P26" s="0">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>6991556100</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0.086599999999999996</v>
+      </c>
+      <c r="D27" s="0">
+        <v>88.75</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0.1026</v>
+      </c>
+      <c r="F27" s="0">
+        <v>105.55</v>
+      </c>
+      <c r="G27" s="0">
+        <v>6876566980</v>
+      </c>
+      <c r="H27" s="0">
+        <v>0.085199999999999998</v>
+      </c>
+      <c r="I27" s="0">
+        <v>87.290000000000006</v>
+      </c>
+      <c r="J27" s="0">
+        <v>0.1009</v>
+      </c>
+      <c r="K27" s="0">
+        <v>103.81</v>
+      </c>
+      <c r="L27" s="0">
+        <v>18213</v>
+      </c>
+      <c r="M27" s="0">
+        <v>4430583</v>
+      </c>
+      <c r="N27" s="0">
+        <v>99010</v>
+      </c>
+      <c r="O27" s="0">
+        <v>377564</v>
+      </c>
+      <c r="P27" s="0">
+        <v>44.75</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>7358659380</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0.088900000000000007</v>
+      </c>
+      <c r="D28" s="0">
+        <v>43.850000000000001</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0.11169999999999999</v>
+      </c>
+      <c r="F28" s="0">
+        <v>56.039999999999999</v>
+      </c>
+      <c r="G28" s="0">
+        <v>7845429660</v>
+      </c>
+      <c r="H28" s="0">
+        <v>0.094799999999999995</v>
+      </c>
+      <c r="I28" s="0">
+        <v>46.75</v>
+      </c>
+      <c r="J28" s="0">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="K28" s="0">
+        <v>59.75</v>
+      </c>
+      <c r="L28" s="0">
+        <v>51130</v>
+      </c>
+      <c r="M28" s="0">
+        <v>1618630</v>
+      </c>
+      <c r="N28" s="0">
+        <v>67874</v>
+      </c>
+      <c r="O28" s="0">
+        <v>153441</v>
+      </c>
+      <c r="P28" s="0">
+        <v>23.850000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>147545086120</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>0.124</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>139.72999999999999</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>0.14799999999999999</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>169.97</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>158215227220</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>0.13300000000000001</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>149.84</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>0.15870000000000001</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>182.27000000000001</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>445923</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>2668061</v>
       </c>
-      <c r="N25" s="0">
+      <c r="N29" s="0">
         <v>124707</v>
       </c>
-      <c r="O25" s="0">
+      <c r="O29" s="0">
         <v>354804</v>
       </c>
-      <c r="P25" s="0">
+      <c r="P29" s="0">
         <v>21.390000000000001</v>
       </c>
     </row>
